--- a/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>-8,59%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 7,48</t>
+          <t>-16,5; 8,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 13,73</t>
+          <t>-11,06; 14,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 8,87</t>
+          <t>-17,46; 9,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 49,26</t>
+          <t>-39,63; 21,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 13,7</t>
+          <t>-24,74; 15,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 26,07</t>
+          <t>-16,17; 26,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 12,89</t>
+          <t>-21,87; 15,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,21; 203,21</t>
+          <t>-44,82; 29,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>-3,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>-4,25%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 5,16</t>
+          <t>-5,53; 5,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,9</t>
+          <t>-7,33; 2,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 6,54</t>
+          <t>-3,72; 6,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 19,35</t>
+          <t>-13,69; 7,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 8,06</t>
+          <t>-7,87; 8,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 4,42</t>
+          <t>-10,56; 4,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 10,59</t>
+          <t>-5,37; 9,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 73,98</t>
+          <t>-16,65; 10,31</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 5,33</t>
+          <t>-12,38; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 12,7</t>
+          <t>-4,83; 13,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 7,59</t>
+          <t>-10,75; 7,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 23,1</t>
+          <t>-15,09; 20,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 9,12</t>
+          <t>-19,94; 11,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 22,37</t>
+          <t>-7,21; 22,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 13,67</t>
+          <t>-16,51; 13,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,39; 151,73</t>
+          <t>-18,07; 30,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 2,79</t>
+          <t>-5,76; 3,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 3,33</t>
+          <t>-4,81; 3,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,43</t>
+          <t>-3,77; 4,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 16,14</t>
+          <t>-10,84; 6,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 4,48</t>
+          <t>-8,59; 5,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 5,24</t>
+          <t>-7,19; 5,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 7,0</t>
+          <t>-5,66; 7,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 61,33</t>
+          <t>-13,03; 9,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 8,69</t>
+          <t>-17,76; 8,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 14,47</t>
+          <t>-10,26; 14,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 9,66</t>
+          <t>-18,51; 8,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 21,58</t>
+          <t>-39,85; 21,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 15,61</t>
+          <t>-26,38; 14,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 26,54</t>
+          <t>-15,15; 28,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 15,07</t>
+          <t>-23,26; 12,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,82; 29,78</t>
+          <t>-44,29; 29,98</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,58</t>
+          <t>-5,0; 5,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 2,91</t>
+          <t>-7,27; 2,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 6,08</t>
+          <t>-3,8; 6,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 7,77</t>
+          <t>-14,5; 7,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 8,73</t>
+          <t>-7,2; 8,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 4,56</t>
+          <t>-10,41; 3,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 9,77</t>
+          <t>-5,68; 11,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 10,31</t>
+          <t>-17,38; 9,93</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 6,03</t>
+          <t>-12,29; 6,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 13,18</t>
+          <t>-4,81; 13,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 7,55</t>
+          <t>-9,91; 7,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 20,22</t>
+          <t>-17,25; 19,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 11,17</t>
+          <t>-19,31; 12,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 22,78</t>
+          <t>-7,41; 22,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 13,62</t>
+          <t>-15,3; 13,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 30,7</t>
+          <t>-19,68; 29,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 3,08</t>
+          <t>-6,09; 2,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,5</t>
+          <t>-4,79; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,62</t>
+          <t>-4,07; 4,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 6,87</t>
+          <t>-11,85; 6,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 5,01</t>
+          <t>-9,24; 4,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,46</t>
+          <t>-6,95; 5,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,4</t>
+          <t>-6,18; 7,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 9,06</t>
+          <t>-14,43; 8,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,43</t>
+          <t>-6,97</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-8,59%</t>
+          <t>-8,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 8,29</t>
+          <t>-18,0; 7,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 14,95</t>
+          <t>-11,97; 13,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 8,02</t>
+          <t>-18,32; 8,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 21,9</t>
+          <t>-35,99; 21,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 14,76</t>
+          <t>-26,42; 13,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 28,41</t>
+          <t>-18,26; 26,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 12,15</t>
+          <t>-23,17; 12,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 29,98</t>
+          <t>-39,69; 28,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,37</t>
+          <t>-5,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,25%</t>
+          <t>-6,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,13</t>
+          <t>-5,37; 5,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 2,61</t>
+          <t>-7,73; 2,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,95</t>
+          <t>-4,35; 6,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 7,42</t>
+          <t>-17,34; 6,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 8,0</t>
+          <t>-7,73; 8,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 3,98</t>
+          <t>-11,13; 4,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 11,25</t>
+          <t>-6,23; 10,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 9,93</t>
+          <t>-21,22; 8,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 6,85</t>
+          <t>-13,17; 5,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 13,34</t>
+          <t>-4,75; 12,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 7,82</t>
+          <t>-10,54; 7,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 19,77</t>
+          <t>-17,46; 20,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 12,79</t>
+          <t>-20,46; 9,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 22,71</t>
+          <t>-7,04; 22,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 13,68</t>
+          <t>-16,45; 13,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 29,6</t>
+          <t>-21,04; 32,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-3,01%</t>
+          <t>-4,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,75</t>
+          <t>-6,07; 2,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 3,31</t>
+          <t>-5,17; 3,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,64</t>
+          <t>-3,55; 4,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 6,58</t>
+          <t>-13,51; 5,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 4,41</t>
+          <t>-9,02; 4,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,26</t>
+          <t>-7,54; 5,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 7,39</t>
+          <t>-5,35; 7,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 8,67</t>
+          <t>-16,1; 6,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,68</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,97</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-6,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-8,02%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-4.516731129906326</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.327073485238395</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.681899685201241</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-6.968295218112985</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07271372340389334</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.02184330774537482</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.06367106450266277</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.08016136642370014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-18,0; 7,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,97; 13,73</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-18,32; 8,87</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-35,99; 21,04</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-26,42; 13,7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-18,26; 26,07</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-23,17; 12,89</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-39,69; 28,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-18.00256399818991</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.96982058349775</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-18.32180496556052</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-35.98568867209297</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2641887043259896</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1825537597241748</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2317023120351348</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.396937854265425</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.477842190622906</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>13.73233021855779</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.872551004278582</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>21.03926165620261</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1369651658253472</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2606712366351856</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1288524534504311</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2850051656030765</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-5,09</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-3,63%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-6,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,37; 5,16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,73; 2,9</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,35; 6,54</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-17,34; 6,32</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,73; 8,06</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-11,13; 4,42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 10,59</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-21,22; 8,14</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.1513817321179389</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.466231773817695</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.33210119822279</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-5.091304203809566</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.002270918948634326</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03633758496303151</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.0204135452129723</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.06425604580251562</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,6</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-2,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.369020448431105</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.725906109990268</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.349825548798893</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-17.34257488613989</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07734990003779491</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1112800066039134</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.06228012834834086</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.21217084518249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,17; 5,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,75; 12,7</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,54; 7,59</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-17,46; 20,54</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-20,46; 9,12</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-7,04; 22,37</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-16,45; 13,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-21,04; 32,63</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.1554250276949</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.901126682785177</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.539221734493641</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.317749691344754</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08064364420628402</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.04424813572722174</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1059222633540332</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.0814027292640605</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,68</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-4,64%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.596367924235089</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.836866571890118</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.420517659778253</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.143070045259131</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.06081038992278529</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.06127622759210348</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.02336783040419318</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.0148842441696694</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,07; 2,79</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,17; 3,33</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 4,43</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 5,25</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-9,02; 4,48</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-7,54; 5,24</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 7,0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-16,1; 6,92</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-13.16739675259827</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.75127216650305</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-10.5401826013858</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-17.46382428456895</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2045613409572949</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.07044226710156012</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.164528394898658</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2103575382454512</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.32723887256402</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.70264148711004</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.586501471485215</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.53859113402536</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.09121177270482937</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2236901344095178</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1366912014606338</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3262628615852161</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.627600960946107</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.6667768214149494</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1766449687071403</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.679345248576305</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02526042670336115</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01012013319359225</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.00272224927411034</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.04643755485914103</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.073982274367736</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.166363877864218</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.551820528158387</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-13.51018343728392</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.09024290441874193</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.07544353164534172</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.05353002302638124</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1609911995992762</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.78763534023503</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.331822048632854</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.433756919314734</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.252570675575955</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04476437618336168</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.05237404446862973</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.06995217201249268</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.06919438222188555</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
